--- a/artfynd/A 56305-2023 artfynd.xlsx
+++ b/artfynd/A 56305-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702736</v>
+        <v>113702860</v>
       </c>
       <c r="B2" t="n">
         <v>96361</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
+          <t>Medbön, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318114</v>
+        <v>317410</v>
       </c>
       <c r="R2" t="n">
-        <v>6514407</v>
+        <v>6514656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702860</v>
+        <v>113702736</v>
       </c>
       <c r="B3" t="n">
         <v>96361</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Medbön, Dls</t>
+          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317410</v>
+        <v>318114</v>
       </c>
       <c r="R3" t="n">
-        <v>6514656</v>
+        <v>6514407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Noomi Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 56305-2023 artfynd.xlsx
+++ b/artfynd/A 56305-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702860</v>
+        <v>113702736</v>
       </c>
       <c r="B2" t="n">
-        <v>96361</v>
+        <v>96365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Medbön, Dls</t>
+          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317410</v>
+        <v>318114</v>
       </c>
       <c r="R2" t="n">
-        <v>6514656</v>
+        <v>6514407</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Noomi Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702736</v>
+        <v>113702860</v>
       </c>
       <c r="B3" t="n">
-        <v>96361</v>
+        <v>96365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
+          <t>Medbön, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318114</v>
+        <v>317410</v>
       </c>
       <c r="R3" t="n">
-        <v>6514407</v>
+        <v>6514656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 56305-2023 artfynd.xlsx
+++ b/artfynd/A 56305-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702736</v>
+        <v>113702860</v>
       </c>
       <c r="B2" t="n">
         <v>96365</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
+          <t>Medbön, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318114</v>
+        <v>317410</v>
       </c>
       <c r="R2" t="n">
-        <v>6514407</v>
+        <v>6514656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702860</v>
+        <v>113702736</v>
       </c>
       <c r="B3" t="n">
         <v>96365</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Medbön, Dls</t>
+          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317410</v>
+        <v>318114</v>
       </c>
       <c r="R3" t="n">
-        <v>6514656</v>
+        <v>6514407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Noomi Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 56305-2023 artfynd.xlsx
+++ b/artfynd/A 56305-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56305-2023 artfynd.xlsx
+++ b/artfynd/A 56305-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113702736</v>
+        <v>113703058</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
+          <t>Medbön, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318114</v>
+        <v>317353</v>
       </c>
       <c r="R2" t="n">
-        <v>6514407</v>
+        <v>6514622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -730,27 +725,27 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Färgelanda</t>
+          <t>Munkedal</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Dalsland</t>
+          <t>Bohuslän</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Lerdal</t>
+          <t>Krokstad</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113702860</v>
+        <v>113702703</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Medbön, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317410</v>
+        <v>317443</v>
       </c>
       <c r="R3" t="n">
-        <v>6514656</v>
+        <v>6514707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +875,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113702736</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>318114</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6514407</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113702860</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Medbön, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>317410</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6514656</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Färgelanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 56305-2023 artfynd.xlsx
+++ b/artfynd/A 56305-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702703</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702736</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,8 +1101,19 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>